--- a/samples/gold/material_gold.xlsx
+++ b/samples/gold/material_gold.xlsx
@@ -31995,7 +31995,7 @@
         </is>
       </c>
       <c r="D13" s="42" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E13" s="44" t="n">
         <v>11</v>
@@ -32009,7 +32009,7 @@
         </is>
       </c>
       <c r="H13" s="42" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I13" s="42" t="n">
         <v>140</v>
